--- a/Team-Data/2013-14/1-8-2013-14.xlsx
+++ b/Team-Data/2013-14/1-8-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,25 +728,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" t="n">
         <v>17</v>
       </c>
       <c r="G2" t="n">
-        <v>0.528</v>
+        <v>0.514</v>
       </c>
       <c r="H2" t="n">
         <v>48.7</v>
       </c>
       <c r="I2" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J2" t="n">
-        <v>82.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>0.459</v>
@@ -688,10 +755,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="O2" t="n">
         <v>16.5</v>
@@ -700,22 +767,22 @@
         <v>21.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.772</v>
+        <v>0.769</v>
       </c>
       <c r="R2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T2" t="n">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="U2" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="V2" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W2" t="n">
         <v>8.6</v>
@@ -727,19 +794,19 @@
         <v>4.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>102</v>
+        <v>102.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -754,7 +821,7 @@
         <v>6</v>
       </c>
       <c r="AI2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ2" t="n">
         <v>17</v>
@@ -772,34 +839,34 @@
         <v>7</v>
       </c>
       <c r="AO2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP2" t="n">
         <v>20</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR2" t="n">
         <v>29</v>
       </c>
       <c r="AS2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW2" t="n">
         <v>9</v>
       </c>
       <c r="AX2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AY2" t="n">
         <v>15</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -843,91 +910,91 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" t="n">
         <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" t="n">
-        <v>0.361</v>
+        <v>0.371</v>
       </c>
       <c r="H3" t="n">
         <v>48</v>
       </c>
       <c r="I3" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J3" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L3" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
         <v>18.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.342</v>
+        <v>0.343</v>
       </c>
       <c r="O3" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="P3" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.759</v>
+        <v>0.761</v>
       </c>
       <c r="R3" t="n">
         <v>10.5</v>
       </c>
       <c r="S3" t="n">
-        <v>31.3</v>
+        <v>31.1</v>
       </c>
       <c r="T3" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U3" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="V3" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="W3" t="n">
         <v>6.7</v>
       </c>
       <c r="X3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>95</v>
+        <v>94.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3.6</v>
+        <v>-3.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF3" t="n">
         <v>23</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>25</v>
       </c>
       <c r="AG3" t="n">
         <v>23</v>
@@ -936,13 +1003,13 @@
         <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ3" t="n">
         <v>25</v>
       </c>
       <c r="AK3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL3" t="n">
         <v>25</v>
@@ -951,16 +1018,16 @@
         <v>25</v>
       </c>
       <c r="AN3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
         <v>20</v>
       </c>
       <c r="AP3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR3" t="n">
         <v>20</v>
@@ -972,7 +1039,7 @@
         <v>23</v>
       </c>
       <c r="AU3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV3" t="n">
         <v>26</v>
@@ -981,22 +1048,22 @@
         <v>27</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
         <v>27</v>
       </c>
       <c r="BB3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
         <v>21</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4</v>
+        <v>0.382</v>
       </c>
       <c r="H4" t="n">
         <v>48.4</v>
@@ -1043,28 +1110,28 @@
         <v>34.6</v>
       </c>
       <c r="J4" t="n">
-        <v>78</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K4" t="n">
         <v>0.443</v>
       </c>
       <c r="L4" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M4" t="n">
         <v>20.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0.365</v>
+        <v>0.368</v>
       </c>
       <c r="O4" t="n">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="P4" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.761</v>
+        <v>0.759</v>
       </c>
       <c r="R4" t="n">
         <v>9.6</v>
@@ -1073,19 +1140,19 @@
         <v>30.1</v>
       </c>
       <c r="T4" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="U4" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="V4" t="n">
         <v>14.6</v>
       </c>
       <c r="W4" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="n">
         <v>4</v>
@@ -1094,28 +1161,28 @@
         <v>22.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.5</v>
+        <v>-4.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF4" t="n">
         <v>19</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1130,37 +1197,37 @@
         <v>16</v>
       </c>
       <c r="AM4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN4" t="n">
         <v>10</v>
       </c>
       <c r="AO4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP4" t="n">
         <v>4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AR4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS4" t="n">
         <v>26</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>27</v>
       </c>
       <c r="AT4" t="n">
         <v>28</v>
       </c>
       <c r="AU4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW4" t="n">
         <v>24</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>21</v>
       </c>
       <c r="AX4" t="n">
         <v>28</v>
@@ -1172,13 +1239,13 @@
         <v>24</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1355,7 @@
         <v>4</v>
       </c>
       <c r="AE5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF5" t="n">
         <v>19</v>
@@ -1297,7 +1364,7 @@
         <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
         <v>28</v>
@@ -1333,7 +1400,7 @@
         <v>13</v>
       </c>
       <c r="AT5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU5" t="n">
         <v>27</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -1467,13 +1534,13 @@
         <v>-0.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF6" t="n">
         <v>16</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>15</v>
       </c>
       <c r="AG6" t="n">
         <v>16</v>
@@ -1500,13 +1567,13 @@
         <v>29</v>
       </c>
       <c r="AO6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP6" t="n">
         <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR6" t="n">
         <v>8</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1716,13 @@
         <v>-5.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
         <v>24</v>
       </c>
       <c r="AF7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG7" t="n">
         <v>25</v>
@@ -1664,7 +1731,7 @@
         <v>1</v>
       </c>
       <c r="AI7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ7" t="n">
         <v>6</v>
@@ -1676,7 +1743,7 @@
         <v>19</v>
       </c>
       <c r="AM7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN7" t="n">
         <v>12</v>
@@ -1688,7 +1755,7 @@
         <v>21</v>
       </c>
       <c r="AQ7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR7" t="n">
         <v>7</v>
@@ -1709,13 +1776,13 @@
         <v>25</v>
       </c>
       <c r="AX7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY7" t="n">
         <v>28</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA7" t="n">
         <v>21</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8" t="n">
         <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G8" t="n">
-        <v>0.556</v>
+        <v>0.571</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
@@ -1771,70 +1838,70 @@
         <v>39.4</v>
       </c>
       <c r="J8" t="n">
-        <v>84.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.466</v>
+        <v>0.468</v>
       </c>
       <c r="L8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="N8" t="n">
         <v>0.369</v>
       </c>
       <c r="O8" t="n">
-        <v>15.6</v>
+        <v>15.9</v>
       </c>
       <c r="P8" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="R8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>30.4</v>
+        <v>30.6</v>
       </c>
       <c r="T8" t="n">
-        <v>40.2</v>
+        <v>40.5</v>
       </c>
       <c r="U8" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="V8" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="W8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X8" t="n">
         <v>4.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z8" t="n">
         <v>20.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>102.7</v>
+        <v>103.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF8" t="n">
         <v>10</v>
@@ -1864,7 +1931,7 @@
         <v>8</v>
       </c>
       <c r="AO8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AP8" t="n">
         <v>28</v>
@@ -1885,7 +1952,7 @@
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1903,10 +1970,10 @@
         <v>30</v>
       </c>
       <c r="BB8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC8" t="n">
         <v>11</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>13</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>0.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
         <v>12</v>
@@ -2037,7 +2104,7 @@
         <v>14</v>
       </c>
       <c r="AL9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM9" t="n">
         <v>13</v>
@@ -2058,10 +2125,10 @@
         <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU9" t="n">
         <v>14</v>
@@ -2073,13 +2140,13 @@
         <v>20</v>
       </c>
       <c r="AX9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -2117,55 +2184,55 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E10" t="n">
         <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G10" t="n">
-        <v>0.389</v>
+        <v>0.4</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J10" t="n">
         <v>85.8</v>
       </c>
       <c r="K10" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L10" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M10" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0.313</v>
+        <v>0.314</v>
       </c>
       <c r="O10" t="n">
         <v>16.3</v>
       </c>
       <c r="P10" t="n">
-        <v>24.8</v>
+        <v>24.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.66</v>
+        <v>0.665</v>
       </c>
       <c r="R10" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="S10" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T10" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="U10" t="n">
         <v>20.3</v>
@@ -2180,43 +2247,43 @@
         <v>5.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>98.8</v>
+        <v>99</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.6</v>
+        <v>-3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
         <v>20</v>
       </c>
       <c r="AF10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH10" t="n">
         <v>14</v>
       </c>
       <c r="AI10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ10" t="n">
         <v>5</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
         <v>27</v>
@@ -2240,16 +2307,16 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2258,19 +2325,19 @@
         <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ10" t="n">
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BB10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -2299,37 +2366,37 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E11" t="n">
         <v>24</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.632</v>
+        <v>0.649</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J11" t="n">
-        <v>84.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="K11" t="n">
         <v>0.465</v>
       </c>
       <c r="L11" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="M11" t="n">
         <v>24.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.388</v>
+        <v>0.389</v>
       </c>
       <c r="O11" t="n">
         <v>15.7</v>
@@ -2341,16 +2408,16 @@
         <v>0.728</v>
       </c>
       <c r="R11" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S11" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="T11" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
       <c r="U11" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="V11" t="n">
         <v>17.3</v>
@@ -2365,28 +2432,28 @@
         <v>4.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="AA11" t="n">
         <v>19.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.4</v>
+        <v>103.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AD11" t="n">
         <v>1</v>
       </c>
       <c r="AE11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AH11" t="n">
         <v>18</v>
@@ -2410,7 +2477,7 @@
         <v>3</v>
       </c>
       <c r="AO11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP11" t="n">
         <v>19</v>
@@ -2419,13 +2486,13 @@
         <v>25</v>
       </c>
       <c r="AR11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="n">
         <v>8</v>
@@ -2440,7 +2507,7 @@
         <v>9</v>
       </c>
       <c r="AY11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ11" t="n">
         <v>26</v>
@@ -2452,7 +2519,7 @@
         <v>8</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F12" t="n">
         <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>0.639</v>
+        <v>0.629</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2499,10 +2566,10 @@
         <v>37.4</v>
       </c>
       <c r="J12" t="n">
-        <v>79.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.473</v>
+        <v>0.474</v>
       </c>
       <c r="L12" t="n">
         <v>9.1</v>
@@ -2511,37 +2578,37 @@
         <v>26.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
       <c r="O12" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="P12" t="n">
-        <v>31.6</v>
+        <v>31.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.699</v>
       </c>
       <c r="R12" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="S12" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="T12" t="n">
-        <v>45.3</v>
+        <v>45.1</v>
       </c>
       <c r="U12" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V12" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="W12" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="X12" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y12" t="n">
         <v>5.5</v>
@@ -2550,16 +2617,16 @@
         <v>20.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>105.8</v>
+        <v>105.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>8</v>
@@ -2568,7 +2635,7 @@
         <v>6</v>
       </c>
       <c r="AG12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH12" t="n">
         <v>14</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2601,7 +2668,7 @@
         <v>29</v>
       </c>
       <c r="AR12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS12" t="n">
         <v>4</v>
@@ -2616,10 +2683,10 @@
         <v>28</v>
       </c>
       <c r="AW12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY12" t="n">
         <v>20</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13" t="n">
         <v>28</v>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8</v>
+        <v>0.824</v>
       </c>
       <c r="H13" t="n">
         <v>48.1</v>
@@ -2681,34 +2748,34 @@
         <v>35.9</v>
       </c>
       <c r="J13" t="n">
-        <v>79.2</v>
+        <v>79</v>
       </c>
       <c r="K13" t="n">
-        <v>0.453</v>
+        <v>0.455</v>
       </c>
       <c r="L13" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M13" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="N13" t="n">
         <v>0.356</v>
       </c>
       <c r="O13" t="n">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="P13" t="n">
-        <v>22.8</v>
+        <v>23.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.788</v>
+        <v>0.787</v>
       </c>
       <c r="R13" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="S13" t="n">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="T13" t="n">
         <v>44.1</v>
@@ -2717,31 +2784,31 @@
         <v>20.6</v>
       </c>
       <c r="V13" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W13" t="n">
         <v>7.5</v>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z13" t="n">
         <v>19.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>97</v>
+        <v>97.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2765,25 +2832,25 @@
         <v>12</v>
       </c>
       <c r="AL13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AN13" t="n">
         <v>14</v>
       </c>
       <c r="AO13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP13" t="n">
         <v>13</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>16</v>
       </c>
       <c r="AQ13" t="n">
         <v>5</v>
       </c>
       <c r="AR13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS13" t="n">
         <v>3</v>
@@ -2795,22 +2862,22 @@
         <v>17</v>
       </c>
       <c r="AV13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AX13" t="n">
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
         <v>20</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -2845,55 +2912,55 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
         <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.658</v>
+        <v>0.649</v>
       </c>
       <c r="H14" t="n">
         <v>48.4</v>
       </c>
       <c r="I14" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J14" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="K14" t="n">
         <v>0.464</v>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M14" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.334</v>
+        <v>0.333</v>
       </c>
       <c r="O14" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="P14" t="n">
-        <v>28.5</v>
+        <v>28.2</v>
       </c>
       <c r="Q14" t="n">
         <v>0.725</v>
       </c>
       <c r="R14" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S14" t="n">
         <v>32.8</v>
       </c>
       <c r="T14" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U14" t="n">
         <v>23.8</v>
@@ -2902,7 +2969,7 @@
         <v>14.2</v>
       </c>
       <c r="W14" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X14" t="n">
         <v>4.6</v>
@@ -2914,10 +2981,10 @@
         <v>21.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>104.8</v>
+        <v>104.6</v>
       </c>
       <c r="AC14" t="n">
         <v>5.1</v>
@@ -2938,7 +3005,7 @@
         <v>18</v>
       </c>
       <c r="AI14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ14" t="n">
         <v>22</v>
@@ -2965,31 +3032,31 @@
         <v>26</v>
       </c>
       <c r="AR14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS14" t="n">
         <v>11</v>
       </c>
       <c r="AT14" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY14" t="n">
         <v>2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA14" t="n">
         <v>2</v>
@@ -2998,7 +3065,7 @@
         <v>6</v>
       </c>
       <c r="BC14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G15" t="n">
-        <v>0.389</v>
+        <v>0.4</v>
       </c>
       <c r="H15" t="n">
         <v>48</v>
@@ -3045,19 +3112,19 @@
         <v>36.8</v>
       </c>
       <c r="J15" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K15" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M15" t="n">
         <v>25.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.363</v>
+        <v>0.364</v>
       </c>
       <c r="O15" t="n">
         <v>16.9</v>
@@ -3066,19 +3133,19 @@
         <v>22.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.742</v>
+        <v>0.74</v>
       </c>
       <c r="R15" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="S15" t="n">
         <v>32.9</v>
       </c>
       <c r="T15" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U15" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V15" t="n">
         <v>15.4</v>
@@ -3087,34 +3154,34 @@
         <v>6.6</v>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Y15" t="n">
         <v>4.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="AA15" t="n">
         <v>19.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5</v>
+        <v>-4.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
         <v>20</v>
       </c>
       <c r="AF15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH15" t="n">
         <v>28</v>
@@ -3123,7 +3190,7 @@
         <v>19</v>
       </c>
       <c r="AJ15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK15" t="n">
         <v>22</v>
@@ -3141,37 +3208,37 @@
         <v>16</v>
       </c>
       <c r="AP15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ15" t="n">
         <v>23</v>
       </c>
       <c r="AR15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS15" t="n">
         <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU15" t="n">
         <v>12</v>
       </c>
       <c r="AV15" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
         <v>28</v>
       </c>
       <c r="AX15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY15" t="n">
         <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA15" t="n">
         <v>25</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -3287,16 +3354,16 @@
         <v>-1.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH16" t="n">
         <v>11</v>
@@ -3320,10 +3387,10 @@
         <v>19</v>
       </c>
       <c r="AO16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ16" t="n">
         <v>18</v>
@@ -3335,7 +3402,7 @@
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AU16" t="n">
         <v>15</v>
@@ -3344,7 +3411,7 @@
         <v>4</v>
       </c>
       <c r="AW16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX16" t="n">
         <v>27</v>
@@ -3353,7 +3420,7 @@
         <v>23</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA16" t="n">
         <v>24</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -3469,22 +3536,22 @@
         <v>7</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
         <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3499,16 +3566,16 @@
         <v>14</v>
       </c>
       <c r="AN17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3669,7 +3736,7 @@
         <v>27</v>
       </c>
       <c r="AJ18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK18" t="n">
         <v>27</v>
@@ -3681,7 +3748,7 @@
         <v>18</v>
       </c>
       <c r="AN18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO18" t="n">
         <v>27</v>
@@ -3696,7 +3763,7 @@
         <v>17</v>
       </c>
       <c r="AS18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT18" t="n">
         <v>26</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -3755,67 +3822,67 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E19" t="n">
         <v>17</v>
       </c>
       <c r="F19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>0.486</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
       </c>
       <c r="I19" t="n">
-        <v>38.7</v>
+        <v>38.9</v>
       </c>
       <c r="J19" t="n">
-        <v>89.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.433</v>
+        <v>0.435</v>
       </c>
       <c r="L19" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M19" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="N19" t="n">
         <v>0.346</v>
       </c>
       <c r="O19" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="P19" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.792</v>
+        <v>0.79</v>
       </c>
       <c r="R19" t="n">
         <v>13.7</v>
       </c>
       <c r="S19" t="n">
-        <v>32.4</v>
+        <v>32.2</v>
       </c>
       <c r="T19" t="n">
-        <v>46.1</v>
+        <v>45.9</v>
       </c>
       <c r="U19" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="V19" t="n">
         <v>14.3</v>
       </c>
       <c r="W19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="X19" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
         <v>5.7</v>
@@ -3824,25 +3891,25 @@
         <v>17.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>107.3</v>
+        <v>107.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE19" t="n">
         <v>12</v>
       </c>
       <c r="AF19" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AG19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH19" t="n">
         <v>20</v>
@@ -3857,13 +3924,13 @@
         <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM19" t="n">
         <v>9</v>
       </c>
       <c r="AN19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="n">
         <v>2</v>
@@ -3878,10 +3945,10 @@
         <v>2</v>
       </c>
       <c r="AS19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU19" t="n">
         <v>6</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -3937,25 +4004,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E20" t="n">
         <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>0.441</v>
+        <v>0.455</v>
       </c>
       <c r="H20" t="n">
         <v>48.6</v>
       </c>
       <c r="I20" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="J20" t="n">
-        <v>85.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="K20" t="n">
         <v>0.456</v>
@@ -3964,73 +4031,73 @@
         <v>6.3</v>
       </c>
       <c r="M20" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0.379</v>
+        <v>0.381</v>
       </c>
       <c r="O20" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P20" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.765</v>
+        <v>0.763</v>
       </c>
       <c r="R20" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S20" t="n">
         <v>30.4</v>
       </c>
       <c r="T20" t="n">
-        <v>43.3</v>
+        <v>43.5</v>
       </c>
       <c r="U20" t="n">
         <v>22.5</v>
       </c>
       <c r="V20" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="W20" t="n">
         <v>8.6</v>
       </c>
       <c r="X20" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Y20" t="n">
         <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>101.7</v>
+        <v>101.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>-1.1</v>
+        <v>-1</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF20" t="n">
         <v>16</v>
       </c>
-      <c r="AF20" t="n">
-        <v>17</v>
-      </c>
       <c r="AG20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ20" t="n">
         <v>4</v>
@@ -4051,7 +4118,7 @@
         <v>15</v>
       </c>
       <c r="AP20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ20" t="n">
         <v>12</v>
@@ -4078,7 +4145,7 @@
         <v>1</v>
       </c>
       <c r="AY20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ20" t="n">
         <v>22</v>
@@ -4090,7 +4157,7 @@
         <v>14</v>
       </c>
       <c r="BC20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -4197,13 +4264,13 @@
         <v>-3.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE21" t="n">
         <v>24</v>
       </c>
       <c r="AF21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG21" t="n">
         <v>24</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR21" t="n">
         <v>19</v>
@@ -4254,25 +4321,25 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX21" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA21" t="n">
         <v>23</v>
       </c>
       <c r="BB21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -4379,19 +4446,19 @@
         <v>7.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
         <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
         <v>8</v>
@@ -4406,10 +4473,10 @@
         <v>22</v>
       </c>
       <c r="AM22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO22" t="n">
         <v>3</v>
@@ -4433,7 +4500,7 @@
         <v>13</v>
       </c>
       <c r="AV22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW22" t="n">
         <v>12</v>
@@ -4442,10 +4509,10 @@
         <v>2</v>
       </c>
       <c r="AY22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA22" t="n">
         <v>12</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -4483,46 +4550,46 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E23" t="n">
         <v>10</v>
       </c>
       <c r="F23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G23" t="n">
-        <v>0.286</v>
+        <v>0.294</v>
       </c>
       <c r="H23" t="n">
         <v>48.6</v>
       </c>
       <c r="I23" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J23" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L23" t="n">
         <v>7.4</v>
       </c>
       <c r="M23" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="N23" t="n">
         <v>0.351</v>
       </c>
       <c r="O23" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="P23" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.749</v>
+        <v>0.748</v>
       </c>
       <c r="R23" t="n">
         <v>9.6</v>
@@ -4537,31 +4604,31 @@
         <v>20.3</v>
       </c>
       <c r="V23" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W23" t="n">
         <v>7.6</v>
       </c>
       <c r="X23" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-4.7</v>
+        <v>-4.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4594,28 +4661,28 @@
         <v>16</v>
       </c>
       <c r="AO23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP23" t="n">
         <v>25</v>
       </c>
-      <c r="AP23" t="n">
-        <v>24</v>
-      </c>
       <c r="AQ23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS23" t="n">
         <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AV23" t="n">
         <v>20</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>16</v>
       </c>
       <c r="AW23" t="n">
         <v>16</v>
@@ -4624,19 +4691,19 @@
         <v>25</v>
       </c>
       <c r="AY23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BA23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB23" t="n">
         <v>23</v>
       </c>
       <c r="BC23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -4743,13 +4810,13 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
         <v>24</v>
       </c>
       <c r="AF24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG24" t="n">
         <v>25</v>
@@ -4764,7 +4831,7 @@
         <v>2</v>
       </c>
       <c r="AK24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL24" t="n">
         <v>18</v>
@@ -4776,10 +4843,10 @@
         <v>28</v>
       </c>
       <c r="AO24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
@@ -4788,13 +4855,13 @@
         <v>10</v>
       </c>
       <c r="AS24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT24" t="n">
         <v>7</v>
       </c>
       <c r="AU24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4803,7 +4870,7 @@
         <v>4</v>
       </c>
       <c r="AX24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY24" t="n">
         <v>30</v>
@@ -4815,7 +4882,7 @@
         <v>16</v>
       </c>
       <c r="BB24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -4847,34 +4914,34 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F25" t="n">
         <v>13</v>
       </c>
       <c r="G25" t="n">
-        <v>0.618</v>
+        <v>0.606</v>
       </c>
       <c r="H25" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="I25" t="n">
         <v>38.2</v>
       </c>
       <c r="J25" t="n">
-        <v>83.5</v>
+        <v>83.3</v>
       </c>
       <c r="K25" t="n">
-        <v>0.457</v>
+        <v>0.459</v>
       </c>
       <c r="L25" t="n">
         <v>9.6</v>
       </c>
       <c r="M25" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="N25" t="n">
         <v>0.369</v>
@@ -4883,25 +4950,25 @@
         <v>17.2</v>
       </c>
       <c r="P25" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q25" t="n">
         <v>0.745</v>
       </c>
       <c r="R25" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S25" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T25" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="U25" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="V25" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W25" t="n">
         <v>8.800000000000001</v>
@@ -4913,7 +4980,7 @@
         <v>4</v>
       </c>
       <c r="Z25" t="n">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="AA25" t="n">
         <v>20.6</v>
@@ -4922,10 +4989,10 @@
         <v>103.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE25" t="n">
         <v>9</v>
@@ -4940,7 +5007,7 @@
         <v>24</v>
       </c>
       <c r="AI25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ25" t="n">
         <v>14</v>
@@ -4961,25 +5028,25 @@
         <v>14</v>
       </c>
       <c r="AP25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ25" t="n">
         <v>22</v>
       </c>
       <c r="AR25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS25" t="n">
         <v>17</v>
       </c>
       <c r="AT25" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
         <v>30</v>
       </c>
       <c r="AV25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW25" t="n">
         <v>5</v>
@@ -4988,7 +5055,7 @@
         <v>8</v>
       </c>
       <c r="AY25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ25" t="n">
         <v>19</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -5029,88 +5096,88 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F26" t="n">
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>0.75</v>
+        <v>0.743</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="J26" t="n">
-        <v>88.3</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L26" t="n">
         <v>10.3</v>
       </c>
       <c r="M26" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="N26" t="n">
-        <v>0.395</v>
+        <v>0.398</v>
       </c>
       <c r="O26" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="P26" t="n">
-        <v>22.3</v>
+        <v>22.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.821</v>
+        <v>0.82</v>
       </c>
       <c r="R26" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S26" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="T26" t="n">
         <v>46.6</v>
       </c>
       <c r="U26" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="V26" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="W26" t="n">
         <v>5.7</v>
       </c>
       <c r="X26" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>109.1</v>
+        <v>109</v>
       </c>
       <c r="AC26" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF26" t="n">
         <v>5</v>
@@ -5140,10 +5207,10 @@
         <v>1</v>
       </c>
       <c r="AO26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -5152,10 +5219,10 @@
         <v>3</v>
       </c>
       <c r="AS26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU26" t="n">
         <v>3</v>
@@ -5176,7 +5243,7 @@
         <v>4</v>
       </c>
       <c r="BA26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BB26" t="n">
         <v>1</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>-3.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE27" t="n">
         <v>28</v>
       </c>
       <c r="AF27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
         <v>27</v>
@@ -5310,19 +5377,19 @@
         <v>13</v>
       </c>
       <c r="AK27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL27" t="n">
         <v>23</v>
       </c>
       <c r="AM27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP27" t="n">
         <v>5</v>
@@ -5337,10 +5404,10 @@
         <v>19</v>
       </c>
       <c r="AT27" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV27" t="n">
         <v>12</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.778</v>
+        <v>0.771</v>
       </c>
       <c r="H28" t="n">
         <v>48.1</v>
       </c>
       <c r="I28" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>84</v>
       </c>
       <c r="K28" t="n">
-        <v>0.489</v>
+        <v>0.488</v>
       </c>
       <c r="L28" t="n">
         <v>8.300000000000001</v>
@@ -5423,31 +5490,31 @@
         <v>21.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.393</v>
+        <v>0.391</v>
       </c>
       <c r="O28" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="P28" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.768</v>
+        <v>0.763</v>
       </c>
       <c r="R28" t="n">
         <v>9.5</v>
       </c>
       <c r="S28" t="n">
-        <v>33.6</v>
+        <v>33.4</v>
       </c>
       <c r="T28" t="n">
-        <v>43.2</v>
+        <v>42.8</v>
       </c>
       <c r="U28" t="n">
         <v>25.2</v>
       </c>
       <c r="V28" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W28" t="n">
         <v>7.8</v>
@@ -5456,25 +5523,25 @@
         <v>4.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="AA28" t="n">
         <v>19</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.8</v>
+        <v>104.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="n">
         <v>2</v>
@@ -5489,16 +5556,16 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN28" t="n">
         <v>2</v>
@@ -5510,28 +5577,28 @@
         <v>29</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR28" t="n">
         <v>28</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW28" t="n">
         <v>15</v>
       </c>
       <c r="AX28" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -5575,94 +5642,94 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F29" t="n">
         <v>17</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5</v>
+        <v>0.485</v>
       </c>
       <c r="H29" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I29" t="n">
         <v>35.9</v>
       </c>
       <c r="J29" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="K29" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L29" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M29" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="N29" t="n">
         <v>0.35</v>
       </c>
       <c r="O29" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="P29" t="n">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.78</v>
+        <v>0.775</v>
       </c>
       <c r="R29" t="n">
         <v>11.6</v>
       </c>
       <c r="S29" t="n">
-        <v>31.1</v>
+        <v>30.8</v>
       </c>
       <c r="T29" t="n">
-        <v>42.7</v>
+        <v>42.3</v>
       </c>
       <c r="U29" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="V29" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W29" t="n">
         <v>7.1</v>
       </c>
       <c r="X29" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Y29" t="n">
         <v>4.9</v>
       </c>
       <c r="Z29" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AA29" t="n">
         <v>22.5</v>
       </c>
-      <c r="AA29" t="n">
-        <v>22.6</v>
-      </c>
       <c r="AB29" t="n">
-        <v>98.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF29" t="n">
         <v>11</v>
       </c>
       <c r="AG29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH29" t="n">
         <v>5</v>
@@ -5671,13 +5738,13 @@
         <v>25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="n">
         <v>23</v>
       </c>
       <c r="AL29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM29" t="n">
         <v>12</v>
@@ -5701,7 +5768,7 @@
         <v>21</v>
       </c>
       <c r="AT29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU29" t="n">
         <v>26</v>
@@ -5710,25 +5777,25 @@
         <v>11</v>
       </c>
       <c r="AW29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX29" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY29" t="n">
         <v>17</v>
       </c>
       <c r="AZ29" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BA29" t="n">
         <v>5</v>
       </c>
       <c r="BB29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -5835,13 +5902,13 @@
         <v>-7.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
         <v>24</v>
       </c>
       <c r="AF30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG30" t="n">
         <v>28</v>
@@ -5868,13 +5935,13 @@
         <v>17</v>
       </c>
       <c r="AO30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR30" t="n">
         <v>12</v>
@@ -5886,13 +5953,13 @@
         <v>25</v>
       </c>
       <c r="AU30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX30" t="n">
         <v>12</v>
@@ -5904,7 +5971,7 @@
         <v>18</v>
       </c>
       <c r="BA30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB30" t="n">
         <v>27</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
         <v>17</v>
       </c>
       <c r="G31" t="n">
-        <v>0.485</v>
+        <v>0.469</v>
       </c>
       <c r="H31" t="n">
         <v>48.9</v>
@@ -5957,43 +6024,43 @@
         <v>37.5</v>
       </c>
       <c r="J31" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L31" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M31" t="n">
         <v>21.1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.384</v>
+        <v>0.381</v>
       </c>
       <c r="O31" t="n">
         <v>15.3</v>
       </c>
       <c r="P31" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="R31" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S31" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="T31" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U31" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V31" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W31" t="n">
         <v>8.5</v>
@@ -6002,22 +6069,22 @@
         <v>4.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6038,16 +6105,16 @@
         <v>10</v>
       </c>
       <c r="AK31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO31" t="n">
         <v>28</v>
@@ -6056,7 +6123,7 @@
         <v>26</v>
       </c>
       <c r="AQ31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR31" t="n">
         <v>14</v>
@@ -6065,34 +6132,34 @@
         <v>18</v>
       </c>
       <c r="AT31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ31" t="n">
         <v>10</v>
       </c>
       <c r="BA31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB31" t="n">
         <v>19</v>
       </c>
       <c r="BC31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-8-2013-14</t>
+          <t>2014-01-08</t>
         </is>
       </c>
     </row>
